--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,12 +914,353 @@
           <t>NSE:BHARATFORG26AUG2260CE</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:07:23</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>7600</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>7600</v>
+      </c>
+      <c r="I6" t="n">
+        <v>208.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>143.64</v>
+      </c>
+      <c r="K6" t="n">
+        <v>265.85</v>
+      </c>
+      <c r="L6" t="n">
+        <v>300.43</v>
+      </c>
+      <c r="M6" t="n">
+        <v>346.54</v>
+      </c>
+      <c r="N6" t="n">
+        <v>240</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="S6" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>53.97</v>
+      </c>
+      <c r="U6" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>NSE:ABB26AUG7600CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:07:23</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1658</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1660</v>
+      </c>
+      <c r="I7" t="n">
+        <v>40</v>
+      </c>
+      <c r="J7" t="n">
+        <v>26.99</v>
+      </c>
+      <c r="K7" t="n">
+        <v>51.62</v>
+      </c>
+      <c r="L7" t="n">
+        <v>58.59</v>
+      </c>
+      <c r="M7" t="n">
+        <v>67.88</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1250</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="S7" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>64.45999999999999</v>
+      </c>
+      <c r="U7" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>NSE:AUROPHARMA26AUG1660CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:07:23</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1078</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1080</v>
+      </c>
+      <c r="I8" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>19.41</v>
+      </c>
+      <c r="K8" t="n">
+        <v>37.37</v>
+      </c>
+      <c r="L8" t="n">
+        <v>42.45</v>
+      </c>
+      <c r="M8" t="n">
+        <v>49.23</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1730</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>0.782</v>
+      </c>
+      <c r="S8" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="T8" t="n">
+        <v>52.35</v>
+      </c>
+      <c r="U8" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NSE:BAJFINANCE26AUG1080CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:07:23</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>2265.2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2260</v>
+      </c>
+      <c r="I9" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="J9" t="n">
+        <v>70.23</v>
+      </c>
+      <c r="K9" t="n">
+        <v>95.53</v>
+      </c>
+      <c r="L9" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="M9" t="n">
+        <v>112.25</v>
+      </c>
+      <c r="N9" t="n">
+        <v>598</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="S9" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>61.07</v>
+      </c>
+      <c r="U9" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Auto Anc</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>NSE:BHARATFORG26AUG2260CE</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1003,6 +1003,11 @@
           <t>NSE:ABB26AUG7600CE</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:10:15</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1171,6 +1176,11 @@
           <t>NSE:BAJFINANCE26AUG1080CE</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:10:15</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1255,12 +1265,436 @@
           <t>NSE:BHARATFORG26AUG2260CE</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:10:15</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>INOXWIND</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>75.48999999999999</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-3.22</v>
+      </c>
+      <c r="H10" t="n">
+        <v>75</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20576</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="S10" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>45.94</v>
+      </c>
+      <c r="U10" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>NSE:INOXWIND26AUG75PE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:10:15</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1240.1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1240</v>
+      </c>
+      <c r="I11" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>32.89</v>
+      </c>
+      <c r="K11" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>58.17</v>
+      </c>
+      <c r="M11" t="n">
+        <v>65.61</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1154</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="S11" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="U11" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>E-Commerce</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>NSE:NAUKRI26AUG1240CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:10:15</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>388</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="H12" t="n">
+        <v>390</v>
+      </c>
+      <c r="I12" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="K12" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="L12" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="M12" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="N12" t="n">
+        <v>7194</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="T12" t="n">
+        <v>61.27</v>
+      </c>
+      <c r="U12" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>NSE:KOTAKBANK26AUG390CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:10:15</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>610</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H13" t="n">
+        <v>610</v>
+      </c>
+      <c r="I13" t="n">
+        <v>27</v>
+      </c>
+      <c r="J13" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="K13" t="n">
+        <v>34.25</v>
+      </c>
+      <c r="L13" t="n">
+        <v>38.59</v>
+      </c>
+      <c r="M13" t="n">
+        <v>44.39</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1851</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>0.623</v>
+      </c>
+      <c r="S13" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="T13" t="n">
+        <v>57.91</v>
+      </c>
+      <c r="U13" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>NSE:KALYANKJIL26AUG610CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:10:15</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GODFRYPHLP</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>2299.8</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2300</v>
+      </c>
+      <c r="I14" t="n">
+        <v>57</v>
+      </c>
+      <c r="J14" t="n">
+        <v>29.23</v>
+      </c>
+      <c r="K14" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="L14" t="n">
+        <v>96.67</v>
+      </c>
+      <c r="M14" t="n">
+        <v>116.51</v>
+      </c>
+      <c r="N14" t="n">
+        <v>877</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="S14" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="T14" t="n">
+        <v>59.69</v>
+      </c>
+      <c r="U14" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>NSE:GODFRYPHLP26AUG2300CE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC14"/>
+  <dimension ref="A1:AC16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1265,6 +1265,11 @@
           <t>NSE:BHARATFORG26AUG2260CE</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:15:48</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1527,6 +1532,11 @@
           <t>NSE:KOTAKBANK26AUG390CE</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:15:48</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1611,6 +1621,11 @@
           <t>NSE:KALYANKJIL26AUG610CE</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:15:48</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1693,6 +1708,184 @@
       <c r="W14" t="inlineStr">
         <is>
           <t>NSE:GODFRYPHLP26AUG2300CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:15:48</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="H15" t="n">
+        <v>13</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="N15" t="n">
+        <v>92592</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>0.5590000000000001</v>
+      </c>
+      <c r="S15" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="T15" t="n">
+        <v>33.89</v>
+      </c>
+      <c r="U15" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Telecom</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>NSE:IDEA26AUG13PE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:15:48</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>170</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H16" t="n">
+        <v>170</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="K16" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="L16" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="M16" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="N16" t="n">
+        <v>9689</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>1.028</v>
+      </c>
+      <c r="S16" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="T16" t="n">
+        <v>79.48</v>
+      </c>
+      <c r="U16" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Auto Anc</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>NSE:MOTHERSON26AUG170CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -1443,6 +1443,16 @@
           <t>NSE:NAUKRI26AUG1240CE</t>
         </is>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:16:21</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC16"/>
+  <dimension ref="A1:AC23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1092,6 +1092,11 @@
           <t>NSE:AUROPHARMA26AUG1660CE</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:18:39</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1354,6 +1359,11 @@
           <t>NSE:INOXWIND26AUG75PE</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:18:39</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1453,6 +1463,11 @@
           <t>Target 1 Hit</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:18:39</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1720,6 +1735,11 @@
           <t>NSE:GODFRYPHLP26AUG2300CE</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:18:39</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1809,6 +1829,11 @@
           <t>NSE:IDEA26AUG13PE</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:18:39</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1896,6 +1921,634 @@
       <c r="W16" t="inlineStr">
         <is>
           <t>NSE:MOTHERSON26AUG170CE</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:18:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:18:38</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>INDUSTOWER</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>371.75</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-3.69</v>
+      </c>
+      <c r="H17" t="n">
+        <v>371</v>
+      </c>
+      <c r="I17" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="K17" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="L17" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="M17" t="n">
+        <v>12.52</v>
+      </c>
+      <c r="N17" t="n">
+        <v>7462</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="S17" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="T17" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Telecom</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>NSE:INDUSTOWER26AUG371PE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:18:38</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>5862.5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H18" t="n">
+        <v>5900</v>
+      </c>
+      <c r="I18" t="n">
+        <v>121.25</v>
+      </c>
+      <c r="J18" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="K18" t="n">
+        <v>159.06</v>
+      </c>
+      <c r="L18" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="M18" t="n">
+        <v>211.99</v>
+      </c>
+      <c r="N18" t="n">
+        <v>412</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="S18" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>77.03</v>
+      </c>
+      <c r="U18" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>NSE:HEROMOTOCO26AUG5900CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:18:38</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1814.9</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1820</v>
+      </c>
+      <c r="I19" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>33.53</v>
+      </c>
+      <c r="K19" t="n">
+        <v>65.65000000000001</v>
+      </c>
+      <c r="L19" t="n">
+        <v>74.73999999999999</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.86</v>
+      </c>
+      <c r="N19" t="n">
+        <v>990</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="S19" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="T19" t="n">
+        <v>80.56</v>
+      </c>
+      <c r="U19" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>NSE:COFORGE26AUG1820CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:18:39</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1468.8</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1460</v>
+      </c>
+      <c r="I20" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>38.79</v>
+      </c>
+      <c r="K20" t="n">
+        <v>64.73999999999999</v>
+      </c>
+      <c r="L20" t="n">
+        <v>72.09</v>
+      </c>
+      <c r="M20" t="n">
+        <v>81.88</v>
+      </c>
+      <c r="N20" t="n">
+        <v>952</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R20" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="S20" t="n">
+        <v>39</v>
+      </c>
+      <c r="T20" t="n">
+        <v>80.48999999999999</v>
+      </c>
+      <c r="U20" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Fintech</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>NSE:PAYTM26AUG1460CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:18:39</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1658.7</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1660</v>
+      </c>
+      <c r="I21" t="n">
+        <v>38.15</v>
+      </c>
+      <c r="J21" t="n">
+        <v>26.79</v>
+      </c>
+      <c r="K21" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="L21" t="n">
+        <v>54.38</v>
+      </c>
+      <c r="M21" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1310</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R21" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="S21" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="T21" t="n">
+        <v>70.18000000000001</v>
+      </c>
+      <c r="U21" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>NSE:TECHM26AUG1660CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:18:39</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1864.5</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1860</v>
+      </c>
+      <c r="I22" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>29.69</v>
+      </c>
+      <c r="K22" t="n">
+        <v>54.51</v>
+      </c>
+      <c r="L22" t="n">
+        <v>61.53</v>
+      </c>
+      <c r="M22" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1168</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R22" t="n">
+        <v>0.873</v>
+      </c>
+      <c r="S22" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>86.56999999999999</v>
+      </c>
+      <c r="U22" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>NSE:LAURUSLABS26AUG1860CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:18:39</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>JUBLFOOD</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>491.15</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H23" t="n">
+        <v>490</v>
+      </c>
+      <c r="I23" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="J23" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="K23" t="n">
+        <v>19.37</v>
+      </c>
+      <c r="L23" t="n">
+        <v>21.58</v>
+      </c>
+      <c r="M23" t="n">
+        <v>24.51</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3184</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R23" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="S23" t="n">
+        <v>44</v>
+      </c>
+      <c r="T23" t="n">
+        <v>75.26000000000001</v>
+      </c>
+      <c r="U23" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>NSE:JUBLFOOD26AUG490CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -1458,9 +1458,14 @@
           <t>2026-08-10 09:16:21</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:19:00</t>
+        </is>
+      </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Target 1 Hit</t>
+          <t>Target 2 Hit</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC23"/>
+  <dimension ref="A1:AC25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2556,6 +2556,190 @@
           <t>NSE:JUBLFOOD26AUG490CE</t>
         </is>
       </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:21:58</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>VBL</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>446.75</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H24" t="n">
+        <v>450</v>
+      </c>
+      <c r="I24" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="J24" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="K24" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="L24" t="n">
+        <v>17.38</v>
+      </c>
+      <c r="M24" t="n">
+        <v>20</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4115</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R24" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="S24" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="T24" t="n">
+        <v>41.56</v>
+      </c>
+      <c r="U24" t="n">
+        <v>41</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>NSE:VBL26AUG450PE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:21:58</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>KAYNES</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>3655.7</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3650</v>
+      </c>
+      <c r="I25" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="J25" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="K25" t="n">
+        <v>127.43</v>
+      </c>
+      <c r="L25" t="n">
+        <v>151.8</v>
+      </c>
+      <c r="M25" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="N25" t="n">
+        <v>576</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R25" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="S25" t="n">
+        <v>40</v>
+      </c>
+      <c r="T25" t="n">
+        <v>66.73999999999999</v>
+      </c>
+      <c r="U25" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>NSE:KAYNES26AUG3650CE</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -1359,11 +1359,6 @@
           <t>NSE:INOXWIND26AUG75PE</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2026-08-10 09:18:39</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2289,6 +2284,11 @@
           <t>NSE:PAYTM26AUG1460CE</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:24:56</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2645,6 +2645,11 @@
           <t>NSE:VBL26AUG450PE</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:24:56</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2734,12 +2739,6 @@
           <t>NSE:KAYNES26AUG3650CE</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr"/>
-      <c r="AC25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC25"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2467,6 +2467,11 @@
           <t>NSE:LAURUSLABS26AUG1860CE</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:27:55</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2737,6 +2742,95 @@
       <c r="W25" t="inlineStr">
         <is>
           <t>NSE:KAYNES26AUG3650CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:27:55</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2224.2</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2220</v>
+      </c>
+      <c r="I26" t="n">
+        <v>56.95</v>
+      </c>
+      <c r="J26" t="n">
+        <v>40.36</v>
+      </c>
+      <c r="K26" t="n">
+        <v>71.76000000000001</v>
+      </c>
+      <c r="L26" t="n">
+        <v>80.65000000000001</v>
+      </c>
+      <c r="M26" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="N26" t="n">
+        <v>877</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R26" t="n">
+        <v>0.734</v>
+      </c>
+      <c r="S26" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="T26" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="U26" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>NSE:HYUNDAI26AUG2220CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -2561,6 +2561,11 @@
           <t>NSE:JUBLFOOD26AUG490CE</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:30:38</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2742,6 +2747,16 @@
       <c r="W25" t="inlineStr">
         <is>
           <t>NSE:KAYNES26AUG3650CE</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:30:39</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -2106,6 +2106,16 @@
           <t>NSE:HEROMOTOCO26AUG5900CE</t>
         </is>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:31:13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -1359,6 +1359,16 @@
           <t>NSE:INOXWIND26AUG75PE</t>
         </is>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:33:32</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2015,6 +2025,11 @@
       <c r="W17" t="inlineStr">
         <is>
           <t>NSE:INDUSTOWER26AUG371PE</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:33:31</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -1364,9 +1364,14 @@
           <t>2026-08-10 09:33:32</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:36:18</t>
+        </is>
+      </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Target 1 Hit</t>
+          <t>Target 2 Hit</t>
         </is>
       </c>
     </row>
@@ -2779,9 +2784,14 @@
           <t>2026-08-10 09:30:39</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:36:18</t>
+        </is>
+      </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Target 1 Hit</t>
+          <t>Target 2 Hit</t>
         </is>
       </c>
     </row>
@@ -2871,6 +2881,11 @@
       <c r="W26" t="inlineStr">
         <is>
           <t>NSE:HYUNDAI26AUG2220CE</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:36:17</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -2794,6 +2794,11 @@
           <t>Target 2 Hit</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:39:04</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -2314,6 +2314,16 @@
           <t>NSE:PAYTM26AUG1460CE</t>
         </is>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:40:03</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
       <c r="AC20" t="inlineStr">
         <is>
           <t>2026-08-10 09:24:56</t>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2032,11 +2032,7 @@
           <t>NSE:INDUSTOWER26AUG371PE</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>2026-08-10 09:33:31</t>
-        </is>
-      </c>
+      <c r="AC17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2901,6 +2897,95 @@
       <c r="AC26" t="inlineStr">
         <is>
           <t>2026-08-10 09:36:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:42:08</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PATANJALI</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>353.15</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="H27" t="n">
+        <v>355</v>
+      </c>
+      <c r="I27" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="J27" t="n">
+        <v>11</v>
+      </c>
+      <c r="K27" t="n">
+        <v>15.83</v>
+      </c>
+      <c r="L27" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="M27" t="n">
+        <v>19.03</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3690</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R27" t="n">
+        <v>0.673</v>
+      </c>
+      <c r="S27" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="T27" t="n">
+        <v>60.48</v>
+      </c>
+      <c r="U27" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>NSE:PATANJALI26AUG355PE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -1374,6 +1374,11 @@
           <t>Target 2 Hit</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:44:48</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2032,7 +2037,6 @@
           <t>NSE:INDUSTOWER26AUG371PE</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2221,6 +2225,11 @@
           <t>NSE:COFORGE26AUG1820CE</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:44:48</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2986,6 +2995,11 @@
       <c r="W27" t="inlineStr">
         <is>
           <t>NSE:PATANJALI26AUG355PE</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:44:48</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -1374,11 +1374,6 @@
           <t>Target 2 Hit</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2026-08-10 09:44:48</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2035,6 +2030,11 @@
       <c r="W17" t="inlineStr">
         <is>
           <t>NSE:INDUSTOWER26AUG371PE</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:47:33</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -2512,11 +2512,7 @@
           <t>NSE:LAURUSLABS26AUG1860CE</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>2026-08-10 09:27:55</t>
-        </is>
-      </c>
+      <c r="AC22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2809,11 +2805,6 @@
           <t>Target 2 Hit</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>2026-08-10 09:39:04</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2995,11 +2986,6 @@
       <c r="W27" t="inlineStr">
         <is>
           <t>NSE:PATANJALI26AUG355PE</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>2026-08-10 09:44:48</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:AC28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2225,11 +2225,6 @@
           <t>NSE:COFORGE26AUG1820CE</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>2026-08-10 09:44:48</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2512,7 +2507,6 @@
           <t>NSE:LAURUSLABS26AUG1860CE</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2805,6 +2799,11 @@
           <t>Target 2 Hit</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:53:03</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2986,6 +2985,100 @@
       <c r="W27" t="inlineStr">
         <is>
           <t>NSE:PATANJALI26AUG355PE</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:53:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:53:03</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>615.95</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H28" t="n">
+        <v>610</v>
+      </c>
+      <c r="I28" t="n">
+        <v>27</v>
+      </c>
+      <c r="J28" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="K28" t="n">
+        <v>34.25</v>
+      </c>
+      <c r="L28" t="n">
+        <v>38.59</v>
+      </c>
+      <c r="M28" t="n">
+        <v>44.39</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1851</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R28" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="S28" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="T28" t="n">
+        <v>58.04</v>
+      </c>
+      <c r="U28" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>NSE:KALYANKJIL26AUG610CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -2319,9 +2319,14 @@
           <t>2026-08-10 09:40:03</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:55:03</t>
+        </is>
+      </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Target 1 Hit</t>
+          <t>Target 2 Hit</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2507,6 +2512,11 @@
           <t>NSE:LAURUSLABS26AUG1860CE</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:56:18</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2987,11 +2997,6 @@
           <t>NSE:PATANJALI26AUG355PE</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>2026-08-10 09:53:03</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3079,6 +3084,11 @@
       <c r="W28" t="inlineStr">
         <is>
           <t>NSE:KALYANKJIL26AUG610CE</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:56:18</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -3086,11 +3086,7 @@
           <t>NSE:KALYANKJIL26AUG610CE</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>2026-08-10 09:56:18</t>
-        </is>
-      </c>
+      <c r="AC28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC28"/>
+  <dimension ref="A1:AC29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2997,6 +2997,11 @@
           <t>NSE:PATANJALI26AUG355PE</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:01:40</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3086,7 +3091,105 @@
           <t>NSE:KALYANKJIL26AUG610CE</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:01:40</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1496.6</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1460</v>
+      </c>
+      <c r="I29" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="J29" t="n">
+        <v>38.79</v>
+      </c>
+      <c r="K29" t="n">
+        <v>64.73999999999999</v>
+      </c>
+      <c r="L29" t="n">
+        <v>72.09</v>
+      </c>
+      <c r="M29" t="n">
+        <v>81.88</v>
+      </c>
+      <c r="N29" t="n">
+        <v>952</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R29" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="S29" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Fintech</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>NSE:PAYTM26AUG1460CE</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:01:44</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -2423,6 +2423,11 @@
           <t>NSE:TECHM26AUG1660CE</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:04:26</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2809,11 +2814,6 @@
           <t>Target 2 Hit</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>2026-08-10 09:53:03</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3185,9 +3185,14 @@
           <t>2026-08-10 10:01:44</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:03:34</t>
+        </is>
+      </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Target 1 Hit</t>
+          <t>Target 2 Hit</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -2423,11 +2423,7 @@
           <t>NSE:TECHM26AUG1660CE</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:04:26</t>
-        </is>
-      </c>
+      <c r="AC21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC29"/>
+  <dimension ref="A1:AC30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2423,7 +2423,11 @@
           <t>NSE:TECHM26AUG1660CE</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:09:58</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3189,6 +3193,90 @@
       <c r="AB29" t="inlineStr">
         <is>
           <t>Target 2 Hit</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:09:58</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>5055.7</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="H30" t="n">
+        <v>5050</v>
+      </c>
+      <c r="I30" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="J30" t="n">
+        <v>70.56999999999999</v>
+      </c>
+      <c r="K30" t="n">
+        <v>126.85</v>
+      </c>
+      <c r="L30" t="n">
+        <v>142.78</v>
+      </c>
+      <c r="M30" t="n">
+        <v>164.02</v>
+      </c>
+      <c r="N30" t="n">
+        <v>498</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="R30" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="S30" t="n">
+        <v>23</v>
+      </c>
+      <c r="T30" t="n">
+        <v>75.62</v>
+      </c>
+      <c r="U30" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>NSE:TITAN26AUG5050CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -2423,11 +2423,7 @@
           <t>NSE:TECHM26AUG1660CE</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:09:58</t>
-        </is>
-      </c>
+      <c r="AC21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC30"/>
+  <dimension ref="A1:AC32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2423,7 +2423,11 @@
           <t>NSE:TECHM26AUG1660CE</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:18:29</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3273,6 +3277,184 @@
       <c r="W30" t="inlineStr">
         <is>
           <t>NSE:TITAN26AUG5050CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:18:29</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="H31" t="n">
+        <v>13</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="N31" t="n">
+        <v>92592</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R31" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="S31" t="n">
+        <v>43</v>
+      </c>
+      <c r="T31" t="n">
+        <v>33.89</v>
+      </c>
+      <c r="U31" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Telecom</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>NSE:IDEA26AUG13PE</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:18:29</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>2232.8</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2220</v>
+      </c>
+      <c r="I32" t="n">
+        <v>56.95</v>
+      </c>
+      <c r="J32" t="n">
+        <v>40.36</v>
+      </c>
+      <c r="K32" t="n">
+        <v>71.76000000000001</v>
+      </c>
+      <c r="L32" t="n">
+        <v>80.65000000000001</v>
+      </c>
+      <c r="M32" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="N32" t="n">
+        <v>877</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R32" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="S32" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="T32" t="n">
+        <v>88</v>
+      </c>
+      <c r="U32" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>NSE:HYUNDAI26AUG2220CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC32"/>
+  <dimension ref="A1:AC40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3457,6 +3457,719 @@
           <t>NSE:HYUNDAI26AUG2220CE</t>
         </is>
       </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:22:18</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>KAYNES</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>3765.8</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-2.35</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3750</v>
+      </c>
+      <c r="I33" t="n">
+        <v>144.95</v>
+      </c>
+      <c r="J33" t="n">
+        <v>98.95</v>
+      </c>
+      <c r="K33" t="n">
+        <v>186.02</v>
+      </c>
+      <c r="L33" t="n">
+        <v>210.66</v>
+      </c>
+      <c r="M33" t="n">
+        <v>243.52</v>
+      </c>
+      <c r="N33" t="n">
+        <v>344</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R33" t="n">
+        <v>0.728</v>
+      </c>
+      <c r="S33" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="T33" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="U33" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>NSE:KAYNES26AUG3750CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:22:18</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>616.9</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H34" t="n">
+        <v>615</v>
+      </c>
+      <c r="I34" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="J34" t="n">
+        <v>21.63</v>
+      </c>
+      <c r="K34" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="L34" t="n">
+        <v>41.22</v>
+      </c>
+      <c r="M34" t="n">
+        <v>46.98</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1683</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R34" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="S34" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="T34" t="n">
+        <v>58.48</v>
+      </c>
+      <c r="U34" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>NSE:KALYANKJIL26AUG615CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:22:19</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>5883.5</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="H35" t="n">
+        <v>5900</v>
+      </c>
+      <c r="I35" t="n">
+        <v>135</v>
+      </c>
+      <c r="J35" t="n">
+        <v>88.91</v>
+      </c>
+      <c r="K35" t="n">
+        <v>176.15</v>
+      </c>
+      <c r="L35" t="n">
+        <v>200.85</v>
+      </c>
+      <c r="M35" t="n">
+        <v>233.77</v>
+      </c>
+      <c r="N35" t="n">
+        <v>370</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R35" t="n">
+        <v>1.007</v>
+      </c>
+      <c r="S35" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="T35" t="n">
+        <v>77.31999999999999</v>
+      </c>
+      <c r="U35" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>NSE:HEROMOTOCO26AUG5900CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:22:19</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H36" t="n">
+        <v>13</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="N36" t="n">
+        <v>108695</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R36" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="S36" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="T36" t="n">
+        <v>33.52</v>
+      </c>
+      <c r="U36" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Telecom</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>NSE:IDEA26AUG13PE</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:22:19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1497.9</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I37" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="J37" t="n">
+        <v>34.85</v>
+      </c>
+      <c r="K37" t="n">
+        <v>60.32</v>
+      </c>
+      <c r="L37" t="n">
+        <v>67.53</v>
+      </c>
+      <c r="M37" t="n">
+        <v>77.14</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1035</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R37" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="S37" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="T37" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Fintech</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>NSE:PAYTM26AUG1500CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:22:19</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1812.3</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1820</v>
+      </c>
+      <c r="I38" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="J38" t="n">
+        <v>33.34</v>
+      </c>
+      <c r="K38" t="n">
+        <v>65.63</v>
+      </c>
+      <c r="L38" t="n">
+        <v>74.77</v>
+      </c>
+      <c r="M38" t="n">
+        <v>86.95</v>
+      </c>
+      <c r="N38" t="n">
+        <v>992</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R38" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="S38" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="T38" t="n">
+        <v>80.54000000000001</v>
+      </c>
+      <c r="U38" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>NSE:COFORGE26AUG1820CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:22:19</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>2239.3</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2240</v>
+      </c>
+      <c r="I39" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="J39" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="K39" t="n">
+        <v>66.88</v>
+      </c>
+      <c r="L39" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="M39" t="n">
+        <v>87</v>
+      </c>
+      <c r="N39" t="n">
+        <v>952</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R39" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="S39" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="T39" t="n">
+        <v>88.22</v>
+      </c>
+      <c r="U39" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>NSE:HYUNDAI26AUG2240CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:22:19</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>5068.8</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="H40" t="n">
+        <v>5050</v>
+      </c>
+      <c r="I40" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="J40" t="n">
+        <v>73.52</v>
+      </c>
+      <c r="K40" t="n">
+        <v>130.64</v>
+      </c>
+      <c r="L40" t="n">
+        <v>146.81</v>
+      </c>
+      <c r="M40" t="n">
+        <v>168.36</v>
+      </c>
+      <c r="N40" t="n">
+        <v>482</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="R40" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="S40" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>75.72</v>
+      </c>
+      <c r="U40" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>NSE:TITAN26AUG5050CE</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC40"/>
+  <dimension ref="A1:AC41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3813,6 +3813,11 @@
           <t>NSE:IDEA26AUG13PE</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:25:20</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4164,12 +4169,95 @@
           <t>NSE:TITAN26AUG5050CE</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="inlineStr"/>
-      <c r="AB40" t="inlineStr"/>
-      <c r="AC40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:25:20</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1661.8</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1660</v>
+      </c>
+      <c r="I41" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="J41" t="n">
+        <v>28.96</v>
+      </c>
+      <c r="K41" t="n">
+        <v>51.56</v>
+      </c>
+      <c r="L41" t="n">
+        <v>57.96</v>
+      </c>
+      <c r="M41" t="n">
+        <v>66.48999999999999</v>
+      </c>
+      <c r="N41" t="n">
+        <v>1222</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R41" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="S41" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="T41" t="n">
+        <v>71.15000000000001</v>
+      </c>
+      <c r="U41" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>NSE:TECHM26AUG1660CE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -3635,6 +3635,11 @@
           <t>NSE:KALYANKJIL26AUG615CE</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:28:13</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -3635,11 +3635,6 @@
           <t>NSE:KALYANKJIL26AUG615CE</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:28:13</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4088,6 +4083,11 @@
       <c r="W39" t="inlineStr">
         <is>
           <t>NSE:HYUNDAI26AUG2240CE</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:30:45</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -3635,6 +3635,11 @@
           <t>NSE:KALYANKJIL26AUG615CE</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:33:15</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4083,11 +4088,6 @@
       <c r="W39" t="inlineStr">
         <is>
           <t>NSE:HYUNDAI26AUG2240CE</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:30:45</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -4090,6 +4090,11 @@
           <t>NSE:HYUNDAI26AUG2240CE</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:35:42</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -3546,6 +3546,11 @@
           <t>NSE:KAYNES26AUG3750CE</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:38:07</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC41"/>
+  <dimension ref="A1:AC46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4273,6 +4273,457 @@
           <t>NSE:TECHM26AUG1660CE</t>
         </is>
       </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:41:41</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>5092.6</v>
+      </c>
+      <c r="G42" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="H42" t="n">
+        <v>5100</v>
+      </c>
+      <c r="I42" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="J42" t="n">
+        <v>63.42</v>
+      </c>
+      <c r="K42" t="n">
+        <v>116.57</v>
+      </c>
+      <c r="L42" t="n">
+        <v>131.61</v>
+      </c>
+      <c r="M42" t="n">
+        <v>151.66</v>
+      </c>
+      <c r="N42" t="n">
+        <v>546</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R42" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="S42" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="T42" t="n">
+        <v>76.48</v>
+      </c>
+      <c r="U42" t="n">
+        <v>51</v>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>NSE:TITAN26AUG5100CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:41:41</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>615</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H43" t="n">
+        <v>615</v>
+      </c>
+      <c r="I43" t="n">
+        <v>29.65</v>
+      </c>
+      <c r="J43" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="K43" t="n">
+        <v>36.84</v>
+      </c>
+      <c r="L43" t="n">
+        <v>41.15</v>
+      </c>
+      <c r="M43" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1686</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R43" t="n">
+        <v>0.578</v>
+      </c>
+      <c r="S43" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="T43" t="n">
+        <v>58.44</v>
+      </c>
+      <c r="U43" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>NSE:KALYANKJIL26AUG615CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:41:41</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>5896</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="H44" t="n">
+        <v>5900</v>
+      </c>
+      <c r="I44" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="J44" t="n">
+        <v>97.38</v>
+      </c>
+      <c r="K44" t="n">
+        <v>187.33</v>
+      </c>
+      <c r="L44" t="n">
+        <v>212.78</v>
+      </c>
+      <c r="M44" t="n">
+        <v>246.72</v>
+      </c>
+      <c r="N44" t="n">
+        <v>345</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S44" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="T44" t="n">
+        <v>77.48</v>
+      </c>
+      <c r="U44" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>NSE:HEROMOTOCO26AUG5900CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:41:41</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1506.5</v>
+      </c>
+      <c r="G45" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I45" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="J45" t="n">
+        <v>38.07</v>
+      </c>
+      <c r="K45" t="n">
+        <v>65.01000000000001</v>
+      </c>
+      <c r="L45" t="n">
+        <v>72.63</v>
+      </c>
+      <c r="M45" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="N45" t="n">
+        <v>956</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R45" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="S45" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="T45" t="n">
+        <v>82.76000000000001</v>
+      </c>
+      <c r="U45" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Fintech</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>NSE:PAYTM26AUG1500CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:41:41</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>1815</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1820</v>
+      </c>
+      <c r="I46" t="n">
+        <v>50.25</v>
+      </c>
+      <c r="J46" t="n">
+        <v>33.11</v>
+      </c>
+      <c r="K46" t="n">
+        <v>65.55</v>
+      </c>
+      <c r="L46" t="n">
+        <v>74.73</v>
+      </c>
+      <c r="M46" t="n">
+        <v>86.98</v>
+      </c>
+      <c r="N46" t="n">
+        <v>995</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R46" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="S46" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="T46" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="U46" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>NSE:COFORGE26AUG1820CE</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC46"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4718,12 +4718,190 @@
           <t>NSE:COFORGE26AUG1820CE</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
-      <c r="AA46" t="inlineStr"/>
-      <c r="AB46" t="inlineStr"/>
-      <c r="AC46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:44:25</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>KAYNES</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>3796.8</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-1.54</v>
+      </c>
+      <c r="H47" t="n">
+        <v>3800</v>
+      </c>
+      <c r="I47" t="n">
+        <v>108</v>
+      </c>
+      <c r="J47" t="n">
+        <v>63</v>
+      </c>
+      <c r="K47" t="n">
+        <v>148.18</v>
+      </c>
+      <c r="L47" t="n">
+        <v>172.28</v>
+      </c>
+      <c r="M47" t="n">
+        <v>204.42</v>
+      </c>
+      <c r="N47" t="n">
+        <v>462</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R47" t="n">
+        <v>0.698</v>
+      </c>
+      <c r="S47" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>76.69</v>
+      </c>
+      <c r="U47" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>NSE:KAYNES26AUG3800CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:44:25</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>2234.7</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H48" t="n">
+        <v>2240</v>
+      </c>
+      <c r="I48" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="J48" t="n">
+        <v>35.55</v>
+      </c>
+      <c r="K48" t="n">
+        <v>65.73999999999999</v>
+      </c>
+      <c r="L48" t="n">
+        <v>74.29000000000001</v>
+      </c>
+      <c r="M48" t="n">
+        <v>85.68000000000001</v>
+      </c>
+      <c r="N48" t="n">
+        <v>970</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R48" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="S48" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="T48" t="n">
+        <v>88.15000000000001</v>
+      </c>
+      <c r="U48" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>NSE:HYUNDAI26AUG2240CE</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -4807,6 +4807,11 @@
           <t>NSE:KAYNES26AUG3800CE</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:46:54</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4896,12 +4901,6 @@
           <t>NSE:HYUNDAI26AUG2240CE</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
-      <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="inlineStr"/>
-      <c r="AA48" t="inlineStr"/>
-      <c r="AB48" t="inlineStr"/>
-      <c r="AC48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AC49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4451,6 +4451,11 @@
           <t>NSE:KALYANKJIL26AUG615CE</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:02</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4807,11 +4812,6 @@
           <t>NSE:KAYNES26AUG3800CE</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:46:54</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4899,6 +4899,90 @@
       <c r="W48" t="inlineStr">
         <is>
           <t>NSE:HYUNDAI26AUG2240CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:54:02</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>INOXWIND</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>74.72</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-4.21</v>
+      </c>
+      <c r="H49" t="n">
+        <v>75</v>
+      </c>
+      <c r="I49" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K49" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="L49" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="M49" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="N49" t="n">
+        <v>19455</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="R49" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="S49" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>38.11</v>
+      </c>
+      <c r="U49" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>NSE:INOXWIND26AUG75PE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -4451,11 +4451,7 @@
           <t>NSE:KALYANKJIL26AUG615CE</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>2026-08-10 10:54:02</t>
-        </is>
-      </c>
+      <c r="AC43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC49"/>
+  <dimension ref="A1:AC50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4451,7 +4451,11 @@
           <t>NSE:KALYANKJIL26AUG615CE</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:01:27</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4979,6 +4983,95 @@
       <c r="W49" t="inlineStr">
         <is>
           <t>NSE:INOXWIND26AUG75PE</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:01:27</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>JUBLFOOD</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>493.95</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="H50" t="n">
+        <v>495</v>
+      </c>
+      <c r="I50" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="J50" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="K50" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="L50" t="n">
+        <v>21</v>
+      </c>
+      <c r="M50" t="n">
+        <v>23.83</v>
+      </c>
+      <c r="N50" t="n">
+        <v>3257</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R50" t="n">
+        <v>1.204</v>
+      </c>
+      <c r="S50" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="T50" t="n">
+        <v>75.73</v>
+      </c>
+      <c r="U50" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>NSE:JUBLFOOD26AUG495CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -4451,11 +4451,6 @@
           <t>NSE:KALYANKJIL26AUG615CE</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:01:27</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4634,6 +4629,16 @@
           <t>NSE:PAYTM26AUG1500CE</t>
         </is>
       </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:03:07</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5072,6 +5077,11 @@
       <c r="W50" t="inlineStr">
         <is>
           <t>NSE:JUBLFOOD26AUG495CE</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:03:52</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC50"/>
+  <dimension ref="A1:AC51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4451,6 +4451,11 @@
           <t>NSE:KALYANKJIL26AUG615CE</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:06:17</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5082,6 +5087,95 @@
       <c r="AC50" t="inlineStr">
         <is>
           <t>2026-08-10 11:03:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:06:17</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>1238.2</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1240</v>
+      </c>
+      <c r="I51" t="n">
+        <v>34.45</v>
+      </c>
+      <c r="J51" t="n">
+        <v>20.59</v>
+      </c>
+      <c r="K51" t="n">
+        <v>46.82</v>
+      </c>
+      <c r="L51" t="n">
+        <v>54.25</v>
+      </c>
+      <c r="M51" t="n">
+        <v>64.15000000000001</v>
+      </c>
+      <c r="N51" t="n">
+        <v>1451</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R51" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="S51" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="T51" t="n">
+        <v>54.52</v>
+      </c>
+      <c r="U51" t="n">
+        <v>41</v>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>NSE:LODHA26AUG1240CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -5178,6 +5178,11 @@
           <t>NSE:LODHA26AUG1240CE</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:08:40</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC51"/>
+  <dimension ref="A1:AC52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5183,6 +5183,101 @@
           <t>2026-08-10 11:08:40</t>
         </is>
       </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:11:08</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>11448</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H52" t="n">
+        <v>11400</v>
+      </c>
+      <c r="I52" t="n">
+        <v>305</v>
+      </c>
+      <c r="J52" t="n">
+        <v>231.54</v>
+      </c>
+      <c r="K52" t="n">
+        <v>370.58</v>
+      </c>
+      <c r="L52" t="n">
+        <v>409.94</v>
+      </c>
+      <c r="M52" t="n">
+        <v>462.4</v>
+      </c>
+      <c r="N52" t="n">
+        <v>163</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R52" t="n">
+        <v>1.112</v>
+      </c>
+      <c r="S52" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="T52" t="n">
+        <v>78.45999999999999</v>
+      </c>
+      <c r="U52" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>NSE:BAJAJHLDNG26AUG11400CE</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC52"/>
+  <dimension ref="A1:AC53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5272,12 +5272,100 @@
           <t>NSE:BAJAJHLDNG26AUG11400CE</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
-      <c r="Y52" t="inlineStr"/>
-      <c r="Z52" t="inlineStr"/>
-      <c r="AA52" t="inlineStr"/>
-      <c r="AB52" t="inlineStr"/>
-      <c r="AC52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:13:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:13:36</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>2680.6</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H53" t="n">
+        <v>2700</v>
+      </c>
+      <c r="I53" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="J53" t="n">
+        <v>58.68</v>
+      </c>
+      <c r="K53" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="L53" t="n">
+        <v>106.81</v>
+      </c>
+      <c r="M53" t="n">
+        <v>120.98</v>
+      </c>
+      <c r="N53" t="n">
+        <v>636</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R53" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="S53" t="n">
+        <v>34</v>
+      </c>
+      <c r="T53" t="n">
+        <v>36.77</v>
+      </c>
+      <c r="U53" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>NSE:MCX26AUG2700PE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -4639,9 +4639,14 @@
           <t>2026-08-10 11:03:07</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:14:49</t>
+        </is>
+      </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Target 1 Hit</t>
+          <t>Target 2 Hit</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC53"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5371,6 +5371,101 @@
           <t>NSE:MCX26AUG2700PE</t>
         </is>
       </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:16:03</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>12.96</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="H54" t="n">
+        <v>13</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="N54" t="n">
+        <v>113636</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R54" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="S54" t="n">
+        <v>43</v>
+      </c>
+      <c r="T54" t="n">
+        <v>35.33</v>
+      </c>
+      <c r="U54" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Telecom</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>NSE:IDEA26AUG13PE</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -5371,6 +5371,11 @@
           <t>NSE:MCX26AUG2700PE</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:18:26</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5460,12 +5465,6 @@
           <t>NSE:IDEA26AUG13PE</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
-      <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="inlineStr"/>
-      <c r="AA54" t="inlineStr"/>
-      <c r="AB54" t="inlineStr"/>
-      <c r="AC54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -4644,9 +4644,14 @@
           <t>2026-08-10 11:14:49</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:25:37</t>
+        </is>
+      </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Target 2 Hit</t>
+          <t>Target 3 Hit</t>
         </is>
       </c>
     </row>
@@ -5463,6 +5468,11 @@
       <c r="W54" t="inlineStr">
         <is>
           <t>NSE:IDEA26AUG13PE</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:25:36</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -5376,6 +5376,16 @@
           <t>NSE:MCX26AUG2700PE</t>
         </is>
       </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:32:52</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AC53" t="inlineStr">
         <is>
           <t>2026-08-10 11:18:26</t>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4743,6 +4743,11 @@
           <t>NSE:COFORGE26AUG1820CE</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:53:58</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5483,6 +5488,95 @@
       <c r="AC54" t="inlineStr">
         <is>
           <t>2026-08-10 11:25:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:53:57</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>454.85</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H55" t="n">
+        <v>455</v>
+      </c>
+      <c r="I55" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J55" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="K55" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="L55" t="n">
+        <v>15.07</v>
+      </c>
+      <c r="M55" t="n">
+        <v>17.36</v>
+      </c>
+      <c r="N55" t="n">
+        <v>4761</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R55" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="S55" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="T55" t="n">
+        <v>56.39</v>
+      </c>
+      <c r="U55" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>NSE:OIL26AUG455PE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5579,6 +5579,101 @@
           <t>NSE:OIL26AUG455PE</t>
         </is>
       </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:58:41</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>INDUSTOWER</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>372.8</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-3.42</v>
+      </c>
+      <c r="H56" t="n">
+        <v>371</v>
+      </c>
+      <c r="I56" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J56" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="K56" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="L56" t="n">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="M56" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="N56" t="n">
+        <v>8196</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R56" t="n">
+        <v>0.544</v>
+      </c>
+      <c r="S56" t="n">
+        <v>26</v>
+      </c>
+      <c r="T56" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Telecom</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>NSE:INDUSTOWER26AUG371PE</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr"/>
+      <c r="AC56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -4743,11 +4743,7 @@
           <t>NSE:COFORGE26AUG1820CE</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:53:58</t>
-        </is>
-      </c>
+      <c r="AC46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5668,12 +5664,6 @@
           <t>NSE:INDUSTOWER26AUG371PE</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
-      <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr"/>
-      <c r="AA56" t="inlineStr"/>
-      <c r="AB56" t="inlineStr"/>
-      <c r="AC56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -4743,7 +4743,11 @@
           <t>NSE:COFORGE26AUG1820CE</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>2026-08-10 12:10:48</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC56"/>
+  <dimension ref="A1:AC57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5668,6 +5668,101 @@
           <t>NSE:INDUSTOWER26AUG371PE</t>
         </is>
       </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-10 12:20:18</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H57" t="n">
+        <v>13</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="N57" t="n">
+        <v>113636</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R57" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="S57" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="T57" t="n">
+        <v>36.36</v>
+      </c>
+      <c r="U57" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Telecom</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>NSE:IDEA26AUG13PE</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr"/>
+      <c r="AC57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -4926,6 +4926,11 @@
           <t>NSE:HYUNDAI26AUG2240CE</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>2026-08-10 12:22:41</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5757,12 +5762,6 @@
           <t>NSE:IDEA26AUG13PE</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
-      <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr"/>
-      <c r="AA57" t="inlineStr"/>
-      <c r="AB57" t="inlineStr"/>
-      <c r="AC57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC57"/>
+  <dimension ref="A1:AC58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5762,6 +5762,101 @@
           <t>NSE:IDEA26AUG13PE</t>
         </is>
       </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-10 12:27:28</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>JUBLFOOD</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>495.45</v>
+      </c>
+      <c r="G58" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H58" t="n">
+        <v>495</v>
+      </c>
+      <c r="I58" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="J58" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="K58" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="L58" t="n">
+        <v>21</v>
+      </c>
+      <c r="M58" t="n">
+        <v>23.83</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3257</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R58" t="n">
+        <v>1.248</v>
+      </c>
+      <c r="S58" t="n">
+        <v>44</v>
+      </c>
+      <c r="T58" t="n">
+        <v>76.14</v>
+      </c>
+      <c r="U58" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>NSE:JUBLFOOD26AUG495CE</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr"/>
+      <c r="AC58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -5762,6 +5762,11 @@
           <t>NSE:IDEA26AUG13PE</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>2026-08-10 12:29:56</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5851,12 +5856,6 @@
           <t>NSE:JUBLFOOD26AUG495CE</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
-      <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="inlineStr"/>
-      <c r="AA58" t="inlineStr"/>
-      <c r="AB58" t="inlineStr"/>
-      <c r="AC58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -4926,11 +4926,7 @@
           <t>NSE:HYUNDAI26AUG2240CE</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>2026-08-10 12:22:41</t>
-        </is>
-      </c>
+      <c r="AC48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5760,11 +5756,6 @@
       <c r="W57" t="inlineStr">
         <is>
           <t>NSE:IDEA26AUG13PE</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>2026-08-10 12:29:56</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -4926,7 +4926,11 @@
           <t>NSE:HYUNDAI26AUG2240CE</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>2026-08-10 12:37:02</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC58"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5851,6 +5851,101 @@
           <t>NSE:JUBLFOOD26AUG495CE</t>
         </is>
       </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-10 12:39:24</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>MAZDOCK</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>2557.7</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H59" t="n">
+        <v>2550</v>
+      </c>
+      <c r="I59" t="n">
+        <v>80.55</v>
+      </c>
+      <c r="J59" t="n">
+        <v>61.67</v>
+      </c>
+      <c r="K59" t="n">
+        <v>97.41</v>
+      </c>
+      <c r="L59" t="n">
+        <v>107.52</v>
+      </c>
+      <c r="M59" t="n">
+        <v>121.01</v>
+      </c>
+      <c r="N59" t="n">
+        <v>620</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R59" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="S59" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="T59" t="n">
+        <v>73.13</v>
+      </c>
+      <c r="U59" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Defence</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>NSE:MAZDOCK26AUG2550CE</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr"/>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr"/>
+      <c r="AB59" t="inlineStr"/>
+      <c r="AC59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5940,12 +5940,101 @@
           <t>NSE:MAZDOCK26AUG2550CE</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
-      <c r="Y59" t="inlineStr"/>
-      <c r="Z59" t="inlineStr"/>
-      <c r="AA59" t="inlineStr"/>
-      <c r="AB59" t="inlineStr"/>
-      <c r="AC59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-10 12:48:50</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>4581.2</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H60" t="n">
+        <v>4600</v>
+      </c>
+      <c r="I60" t="n">
+        <v>119.75</v>
+      </c>
+      <c r="J60" t="n">
+        <v>84.39</v>
+      </c>
+      <c r="K60" t="n">
+        <v>151.32</v>
+      </c>
+      <c r="L60" t="n">
+        <v>170.27</v>
+      </c>
+      <c r="M60" t="n">
+        <v>195.53</v>
+      </c>
+      <c r="N60" t="n">
+        <v>417</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R60" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="S60" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="T60" t="n">
+        <v>77.33</v>
+      </c>
+      <c r="U60" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Alcohol</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>NSE:RADICO26AUG4600CE</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr"/>
+      <c r="AC60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC60"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6029,12 +6029,100 @@
           <t>NSE:RADICO26AUG4600CE</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
-      <c r="Y60" t="inlineStr"/>
-      <c r="Z60" t="inlineStr"/>
-      <c r="AA60" t="inlineStr"/>
-      <c r="AB60" t="inlineStr"/>
-      <c r="AC60" t="inlineStr"/>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>2026-08-10 12:53:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-10 12:53:34</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1807.1</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1820</v>
+      </c>
+      <c r="I61" t="n">
+        <v>50.25</v>
+      </c>
+      <c r="J61" t="n">
+        <v>33.11</v>
+      </c>
+      <c r="K61" t="n">
+        <v>65.55</v>
+      </c>
+      <c r="L61" t="n">
+        <v>74.73</v>
+      </c>
+      <c r="M61" t="n">
+        <v>86.98</v>
+      </c>
+      <c r="N61" t="n">
+        <v>995</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R61" t="n">
+        <v>0.847</v>
+      </c>
+      <c r="S61" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="T61" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>NSE:COFORGE26AUG1820CE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -5762,6 +5762,11 @@
           <t>NSE:IDEA26AUG13PE</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>2026-08-10 13:07:04</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5762,11 +5762,7 @@
           <t>NSE:IDEA26AUG13PE</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>2026-08-10 13:07:04</t>
-        </is>
-      </c>
+      <c r="AC57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6126,6 +6122,95 @@
       <c r="W61" t="inlineStr">
         <is>
           <t>NSE:COFORGE26AUG1820CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-10 13:14:10</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>1932</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1940</v>
+      </c>
+      <c r="I62" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="J62" t="n">
+        <v>26.09</v>
+      </c>
+      <c r="K62" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="L62" t="n">
+        <v>60.23</v>
+      </c>
+      <c r="M62" t="n">
+        <v>70.27</v>
+      </c>
+      <c r="N62" t="n">
+        <v>1245</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R62" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="S62" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="T62" t="n">
+        <v>30.97</v>
+      </c>
+      <c r="U62" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>NSE:PHOENIXLTD26AUG1940PE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -5762,7 +5762,11 @@
           <t>NSE:IDEA26AUG13PE</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr"/>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>2026-08-10 13:16:33</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -4837,6 +4837,21 @@
           <t>NSE:KAYNES26AUG3800CE</t>
         </is>
       </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>2026-08-10 13:28:02</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>2026-08-10 13:28:48</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -5871,6 +5871,11 @@
           <t>NSE:JUBLFOOD26AUG495CE</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>2026-08-10 13:31:28</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6230,6 +6235,11 @@
       <c r="W62" t="inlineStr">
         <is>
           <t>NSE:PHOENIXLTD26AUG1940PE</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>2026-08-10 13:31:27</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -5777,11 +5777,6 @@
           <t>NSE:IDEA26AUG13PE</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>2026-08-10 13:16:33</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5963,6 +5958,11 @@
       <c r="W59" t="inlineStr">
         <is>
           <t>NSE:MAZDOCK26AUG2550CE</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>2026-08-10 13:39:17</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -5777,6 +5777,11 @@
           <t>NSE:IDEA26AUG13PE</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>2026-08-10 13:41:47</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC62"/>
+  <dimension ref="A1:AC63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5871,11 +5871,7 @@
           <t>NSE:JUBLFOOD26AUG495CE</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>2026-08-10 13:31:28</t>
-        </is>
-      </c>
+      <c r="AC58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6245,6 +6241,95 @@
       <c r="AC62" t="inlineStr">
         <is>
           <t>2026-08-10 13:31:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-10 13:44:25</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SUZLON</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>47.17</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="H63" t="n">
+        <v>47</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="L63" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M63" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="N63" t="n">
+        <v>40322</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R63" t="n">
+        <v>0.534</v>
+      </c>
+      <c r="S63" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="T63" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="U63" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>NSE:SUZLON26AUG47PE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC63"/>
+  <dimension ref="A1:AC64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5871,7 +5871,11 @@
           <t>NSE:JUBLFOOD26AUG495CE</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr"/>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:02:26</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6330,6 +6334,95 @@
       <c r="W63" t="inlineStr">
         <is>
           <t>NSE:SUZLON26AUG47PE</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:02:25</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>KAYNES</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>3728.1</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-3.32</v>
+      </c>
+      <c r="H64" t="n">
+        <v>3750</v>
+      </c>
+      <c r="I64" t="n">
+        <v>90</v>
+      </c>
+      <c r="J64" t="n">
+        <v>46.76</v>
+      </c>
+      <c r="K64" t="n">
+        <v>128.61</v>
+      </c>
+      <c r="L64" t="n">
+        <v>151.77</v>
+      </c>
+      <c r="M64" t="n">
+        <v>182.66</v>
+      </c>
+      <c r="N64" t="n">
+        <v>555</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R64" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="S64" t="n">
+        <v>38</v>
+      </c>
+      <c r="T64" t="n">
+        <v>72.34999999999999</v>
+      </c>
+      <c r="U64" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>NSE:KAYNES26AUG3750CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC64"/>
+  <dimension ref="A1:AC65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6153,6 +6153,11 @@
           <t>NSE:COFORGE26AUG1820CE</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:05:13</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6423,6 +6428,95 @@
       <c r="W64" t="inlineStr">
         <is>
           <t>NSE:KAYNES26AUG3750CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:05:13</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>1933.4</v>
+      </c>
+      <c r="G65" t="n">
+        <v>2</v>
+      </c>
+      <c r="H65" t="n">
+        <v>1940</v>
+      </c>
+      <c r="I65" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="J65" t="n">
+        <v>26.09</v>
+      </c>
+      <c r="K65" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="L65" t="n">
+        <v>60.23</v>
+      </c>
+      <c r="M65" t="n">
+        <v>70.27</v>
+      </c>
+      <c r="N65" t="n">
+        <v>1245</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R65" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="S65" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="T65" t="n">
+        <v>32.02</v>
+      </c>
+      <c r="U65" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>NSE:PHOENIXLTD26AUG1940PE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -6519,6 +6519,11 @@
           <t>NSE:PHOENIXLTD26AUG1940PE</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:07:53</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -6430,6 +6430,11 @@
           <t>NSE:KAYNES26AUG3750CE</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:32:45</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC65"/>
+  <dimension ref="A1:AC66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6529,6 +6529,96 @@
           <t>2026-08-10 14:07:53</t>
         </is>
       </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:38:19</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>2082.9</v>
+      </c>
+      <c r="G66" t="n">
+        <v>-8.050000000000001</v>
+      </c>
+      <c r="H66" t="n">
+        <v>2080</v>
+      </c>
+      <c r="I66" t="n">
+        <v>68.84999999999999</v>
+      </c>
+      <c r="J66" t="n">
+        <v>51.52</v>
+      </c>
+      <c r="K66" t="n">
+        <v>84.31999999999999</v>
+      </c>
+      <c r="L66" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="M66" t="n">
+        <v>105.98</v>
+      </c>
+      <c r="N66" t="n">
+        <v>726</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="R66" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S66" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>36.31</v>
+      </c>
+      <c r="U66" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Auto Anc</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>NSE:BHARATFORG26AUG2080CE</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr"/>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr"/>
+      <c r="AC66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -6613,12 +6613,11 @@
           <t>NSE:BHARATFORG26AUG2080CE</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr"/>
-      <c r="Y66" t="inlineStr"/>
-      <c r="Z66" t="inlineStr"/>
-      <c r="AA66" t="inlineStr"/>
-      <c r="AB66" t="inlineStr"/>
-      <c r="AC66" t="inlineStr"/>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:41:06</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC66"/>
+  <dimension ref="A1:AC67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6341,6 +6341,11 @@
           <t>NSE:SUZLON26AUG47PE</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:43:52</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6613,9 +6618,93 @@
           <t>NSE:BHARATFORG26AUG2080CE</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>2026-08-10 14:41:06</t>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:43:52</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1099.3</v>
+      </c>
+      <c r="G67" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1100</v>
+      </c>
+      <c r="I67" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="J67" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="K67" t="n">
+        <v>32.91</v>
+      </c>
+      <c r="L67" t="n">
+        <v>38.23</v>
+      </c>
+      <c r="M67" t="n">
+        <v>45.32</v>
+      </c>
+      <c r="N67" t="n">
+        <v>2079</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R67" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="S67" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="T67" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="U67" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>NSE:BAJFINANCE26AUG1100CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -6707,6 +6707,11 @@
           <t>NSE:BAJFINANCE26AUG1100CE</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:46:37</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC67"/>
+  <dimension ref="A1:AC68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5030,6 +5030,16 @@
           <t>NSE:INOXWIND26AUG75PE</t>
         </is>
       </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:49:30</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6707,9 +6717,93 @@
           <t>NSE:BAJFINANCE26AUG1100CE</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>2026-08-10 14:46:37</t>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:49:27</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>MAZDOCK</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>2564.2</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H68" t="n">
+        <v>2550</v>
+      </c>
+      <c r="I68" t="n">
+        <v>80.55</v>
+      </c>
+      <c r="J68" t="n">
+        <v>61.67</v>
+      </c>
+      <c r="K68" t="n">
+        <v>97.41</v>
+      </c>
+      <c r="L68" t="n">
+        <v>107.52</v>
+      </c>
+      <c r="M68" t="n">
+        <v>121.01</v>
+      </c>
+      <c r="N68" t="n">
+        <v>620</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R68" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="S68" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="T68" t="n">
+        <v>73.39</v>
+      </c>
+      <c r="U68" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Defence</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>NSE:MAZDOCK26AUG2550CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -6717,6 +6717,11 @@
           <t>NSE:BAJFINANCE26AUG1100CE</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:52:15</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6804,6 +6809,11 @@
       <c r="W68" t="inlineStr">
         <is>
           <t>NSE:MAZDOCK26AUG2550CE</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:52:16</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -4451,6 +4451,16 @@
           <t>NSE:KALYANKJIL26AUG615CE</t>
         </is>
       </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:54:58</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AC43" t="inlineStr">
         <is>
           <t>2026-08-10 11:06:17</t>
@@ -6717,11 +6727,7 @@
           <t>NSE:BAJFINANCE26AUG1100CE</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>2026-08-10 14:52:15</t>
-        </is>
-      </c>
+      <c r="AC67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -6638,6 +6638,11 @@
           <t>NSE:BHARATFORG26AUG2080CE</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:57:53</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6727,7 +6732,6 @@
           <t>NSE:BAJFINANCE26AUG1100CE</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6815,11 +6819,6 @@
       <c r="W68" t="inlineStr">
         <is>
           <t>NSE:MAZDOCK26AUG2550CE</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>2026-08-10 14:52:16</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -5708,6 +5708,16 @@
           <t>NSE:INDUSTOWER26AUG371PE</t>
         </is>
       </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:59:30</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5797,6 +5807,16 @@
           <t>NSE:IDEA26AUG13PE</t>
         </is>
       </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:59:30</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
       <c r="AC57" t="inlineStr">
         <is>
           <t>2026-08-10 13:41:47</t>
@@ -6455,11 +6475,7 @@
           <t>NSE:KAYNES26AUG3750CE</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>2026-08-10 14:32:45</t>
-        </is>
-      </c>
+      <c r="AC64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC68"/>
+  <dimension ref="A1:AC70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5619,6 +5619,11 @@
           <t>NSE:OIL26AUG455PE</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:11:56</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6475,7 +6480,6 @@
           <t>NSE:KAYNES26AUG3750CE</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6835,6 +6839,184 @@
       <c r="W68" t="inlineStr">
         <is>
           <t>NSE:MAZDOCK26AUG2550CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:11:56</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>2778</v>
+      </c>
+      <c r="G69" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="H69" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I69" t="n">
+        <v>89.95</v>
+      </c>
+      <c r="J69" t="n">
+        <v>68.14</v>
+      </c>
+      <c r="K69" t="n">
+        <v>109.42</v>
+      </c>
+      <c r="L69" t="n">
+        <v>121.11</v>
+      </c>
+      <c r="M69" t="n">
+        <v>136.69</v>
+      </c>
+      <c r="N69" t="n">
+        <v>555</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R69" t="n">
+        <v>0.658</v>
+      </c>
+      <c r="S69" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="T69" t="n">
+        <v>48.01</v>
+      </c>
+      <c r="U69" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>NSE:MCX26AUG2800PE</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:11:56</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>JUBLFOOD</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>496.55</v>
+      </c>
+      <c r="G70" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="H70" t="n">
+        <v>495</v>
+      </c>
+      <c r="I70" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="J70" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="K70" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="L70" t="n">
+        <v>21</v>
+      </c>
+      <c r="M70" t="n">
+        <v>23.83</v>
+      </c>
+      <c r="N70" t="n">
+        <v>3257</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R70" t="n">
+        <v>1.227</v>
+      </c>
+      <c r="S70" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="T70" t="n">
+        <v>76.12</v>
+      </c>
+      <c r="U70" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>NSE:JUBLFOOD26AUG495CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC70"/>
+  <dimension ref="A1:AC71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4555,6 +4555,11 @@
           <t>NSE:HEROMOTOCO26AUG5900CE</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:14:47</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5619,11 +5624,6 @@
           <t>NSE:OIL26AUG455PE</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>2026-08-10 15:11:56</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6480,6 +6480,11 @@
           <t>NSE:KAYNES26AUG3750CE</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:14:47</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7017,6 +7022,100 @@
       <c r="W70" t="inlineStr">
         <is>
           <t>NSE:JUBLFOOD26AUG495CE</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:14:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:14:46</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>3392</v>
+      </c>
+      <c r="G71" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H71" t="n">
+        <v>3380</v>
+      </c>
+      <c r="I71" t="n">
+        <v>99.45</v>
+      </c>
+      <c r="J71" t="n">
+        <v>76.94</v>
+      </c>
+      <c r="K71" t="n">
+        <v>119.54</v>
+      </c>
+      <c r="L71" t="n">
+        <v>131.6</v>
+      </c>
+      <c r="M71" t="n">
+        <v>147.67</v>
+      </c>
+      <c r="N71" t="n">
+        <v>502</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R71" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="S71" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="T71" t="n">
+        <v>64.88</v>
+      </c>
+      <c r="U71" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>NSE:GRASIM26AUG3380CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -7118,6 +7118,11 @@
           <t>NSE:GRASIM26AUG3380CE</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:17:32</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -5817,9 +5817,14 @@
           <t>2026-08-10 14:59:30</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:22:57</t>
+        </is>
+      </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>Target 1 Hit</t>
+          <t>Target 2 Hit</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -4555,11 +4555,7 @@
           <t>NSE:HEROMOTOCO26AUG5900CE</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>2026-08-10 15:14:47</t>
-        </is>
-      </c>
+      <c r="AC44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6483,11 +6479,6 @@
       <c r="W64" t="inlineStr">
         <is>
           <t>NSE:KAYNES26AUG3750CE</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>2026-08-10 15:14:47</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -662,6 +662,16 @@
           <t>NSE:ABB26AUG7600CE</t>
         </is>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2026-08-10 13:37:00</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -830,6 +840,16 @@
           <t>NSE:BAJFINANCE26AUG1080CE</t>
         </is>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:09:00</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -914,6 +934,16 @@
           <t>NSE:BHARATFORG26AUG2260CE</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:21:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1003,6 +1033,16 @@
           <t>NSE:ABB26AUG7600CE</t>
         </is>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-10 13:37:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
           <t>2026-08-10 09:10:15</t>
@@ -1181,6 +1221,16 @@
           <t>NSE:BAJFINANCE26AUG1080CE</t>
         </is>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:09:00</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
           <t>2026-08-10 09:10:15</t>
@@ -1270,6 +1320,16 @@
           <t>NSE:BHARATFORG26AUG2260CE</t>
         </is>
       </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:21:00</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
           <t>2026-08-10 09:15:48</t>
@@ -1844,6 +1904,16 @@
           <t>NSE:IDEA26AUG13PE</t>
         </is>
       </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:19:00</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
           <t>2026-08-10 09:18:39</t>
@@ -1938,6 +2008,16 @@
           <t>NSE:MOTHERSON26AUG170CE</t>
         </is>
       </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:26:00</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
           <t>2026-08-10 09:18:39</t>
@@ -2032,6 +2112,16 @@
           <t>NSE:INDUSTOWER26AUG371PE</t>
         </is>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:59:00</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
       <c r="AC17" t="inlineStr">
         <is>
           <t>2026-08-10 09:47:33</t>
@@ -2423,6 +2513,16 @@
           <t>NSE:TECHM26AUG1660CE</t>
         </is>
       </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:55:00</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AC21" t="inlineStr">
         <is>
           <t>2026-08-10 10:18:29</t>
@@ -2611,6 +2711,16 @@
           <t>NSE:JUBLFOOD26AUG490CE</t>
         </is>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-10 12:30:00</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
       <c r="AC23" t="inlineStr">
         <is>
           <t>2026-08-10 09:30:38</t>
@@ -2997,6 +3107,16 @@
           <t>NSE:PATANJALI26AUG355PE</t>
         </is>
       </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:20:00</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AC27" t="inlineStr">
         <is>
           <t>2026-08-10 10:01:40</t>
@@ -3279,6 +3399,16 @@
           <t>NSE:TITAN26AUG5050CE</t>
         </is>
       </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:45:00</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3368,6 +3498,16 @@
           <t>NSE:IDEA26AUG13PE</t>
         </is>
       </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:19:00</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3546,6 +3686,16 @@
           <t>NSE:KAYNES26AUG3750CE</t>
         </is>
       </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:01:00</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AC33" t="inlineStr">
         <is>
           <t>2026-08-10 10:38:07</t>
@@ -3640,6 +3790,16 @@
           <t>NSE:KALYANKJIL26AUG615CE</t>
         </is>
       </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:54:00</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AC34" t="inlineStr">
         <is>
           <t>2026-08-10 10:33:15</t>
@@ -3823,6 +3983,21 @@
           <t>NSE:IDEA26AUG13PE</t>
         </is>
       </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:15:00</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:28:00</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>Target 2 Hit</t>
+        </is>
+      </c>
       <c r="AC36" t="inlineStr">
         <is>
           <t>2026-08-10 10:25:20</t>
@@ -3917,6 +4092,26 @@
           <t>NSE:PAYTM26AUG1500CE</t>
         </is>
       </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:01:00</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:06:00</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:15:00</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>Target 3 Hit</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4184,6 +4379,16 @@
           <t>NSE:TITAN26AUG5050CE</t>
         </is>
       </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:46:00</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4273,6 +4478,16 @@
           <t>NSE:TECHM26AUG1660CE</t>
         </is>
       </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>2026-08-10 13:52:00</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4555,7 +4770,6 @@
           <t>NSE:HEROMOTOCO26AUG5900CE</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5524,6 +5738,21 @@
       <c r="W54" t="inlineStr">
         <is>
           <t>NSE:IDEA26AUG13PE</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:59:00</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:23:00</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>Target 2 Hit</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">

--- a/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
+++ b/backend/signal_logs/2026-08-10/signals_2026-08-10.xlsx
@@ -756,6 +756,11 @@
           <t>NSE:AUROPHARMA26AUG1660CE</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Closed down ~28.2 (-29.5% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1132,6 +1137,11 @@
           <t>NSE:AUROPHARMA26AUG1660CE</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Closed up ~44.2 (+10.5% from entry)</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
           <t>2026-08-10 09:18:39</t>
@@ -1632,6 +1642,11 @@
           <t>NSE:KOTAKBANK26AUG390CE</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Closed up ~8.1 (+16.6% from entry, EOD estimate)</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
           <t>2026-08-10 09:15:48</t>
@@ -1721,6 +1736,11 @@
           <t>NSE:KALYANKJIL26AUG610CE</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Closed up ~27.75 (+2.8% from entry)</t>
+        </is>
+      </c>
       <c r="AC13" t="inlineStr">
         <is>
           <t>2026-08-10 09:15:48</t>
@@ -1810,6 +1830,11 @@
           <t>NSE:GODFRYPHLP26AUG2300CE</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Closed down ~48.9 (-14.2% from entry, EOD estimate)</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
           <t>2026-08-10 09:18:39</t>
@@ -2315,6 +2340,11 @@
           <t>NSE:COFORGE26AUG1820CE</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>Closed down ~44.3 (-12.3% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2617,6 +2647,11 @@
           <t>NSE:LAURUSLABS26AUG1860CE</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>Closed up ~43.5 (+1.6% from entry)</t>
+        </is>
+      </c>
       <c r="AC22" t="inlineStr">
         <is>
           <t>2026-08-10 09:56:18</t>
@@ -2815,6 +2850,11 @@
           <t>NSE:VBL26AUG450PE</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>Closed flat ~12.2 (+0.4% from entry)</t>
+        </is>
+      </c>
       <c r="AC24" t="inlineStr">
         <is>
           <t>2026-08-10 09:24:56</t>
@@ -3013,6 +3053,11 @@
           <t>NSE:HYUNDAI26AUG2220CE</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>Closed down ~54.75 (-3.9% from entry)</t>
+        </is>
+      </c>
       <c r="AC26" t="inlineStr">
         <is>
           <t>2026-08-10 09:36:17</t>
@@ -3211,6 +3256,11 @@
           <t>NSE:KALYANKJIL26AUG610CE</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>Closed down ~23.9 (-11.5% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3597,6 +3647,11 @@
           <t>NSE:HYUNDAI26AUG2220CE</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>Closed down ~54.5 (-4.3% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3894,6 +3949,11 @@
           <t>NSE:HEROMOTOCO26AUG5900CE</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>Closed down ~122.05 (-9.6% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4201,6 +4261,11 @@
           <t>NSE:COFORGE26AUG1820CE</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>Closed down ~44.3 (-12.1% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4290,6 +4355,11 @@
           <t>NSE:HYUNDAI26AUG2240CE</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>Closed down ~43.95 (-16.3% from entry)</t>
+        </is>
+      </c>
       <c r="AC39" t="inlineStr">
         <is>
           <t>2026-08-10 10:35:42</t>
@@ -4577,6 +4647,11 @@
           <t>NSE:TITAN26AUG5100CE</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>Closed down ~89.5 (-2.2% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4770,6 +4845,11 @@
           <t>NSE:HEROMOTOCO26AUG5900CE</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>Closed down ~122.05 (-15.8% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4968,6 +5048,11 @@
           <t>NSE:COFORGE26AUG1820CE</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>Closed down ~45.0 (-10.4% from entry)</t>
+        </is>
+      </c>
       <c r="AC46" t="inlineStr">
         <is>
           <t>2026-08-10 12:10:48</t>
@@ -5166,6 +5251,11 @@
           <t>NSE:HYUNDAI26AUG2240CE</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>Closed flat ~51.45 (-0.1% from entry)</t>
+        </is>
+      </c>
       <c r="AC48" t="inlineStr">
         <is>
           <t>2026-08-10 12:37:02</t>
@@ -5354,6 +5444,11 @@
           <t>NSE:JUBLFOOD26AUG495CE</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>Closed down ~15.25 (-0.7% from entry)</t>
+        </is>
+      </c>
       <c r="AC50" t="inlineStr">
         <is>
           <t>2026-08-10 11:03:52</t>
@@ -5448,6 +5543,11 @@
           <t>NSE:LODHA26AUG1240CE</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>Closed down ~33.75 (-2.0% from entry)</t>
+        </is>
+      </c>
       <c r="AC51" t="inlineStr">
         <is>
           <t>2026-08-10 11:08:40</t>
@@ -5542,6 +5642,11 @@
           <t>NSE:BAJAJHLDNG26AUG11400CE</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>Closed down ~303.35 (-0.5% from entry)</t>
+        </is>
+      </c>
       <c r="AC52" t="inlineStr">
         <is>
           <t>2026-08-10 11:13:36</t>
@@ -5849,6 +5954,11 @@
           <t>NSE:OIL26AUG455PE</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>Closed down ~10.2 (-2.9% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6146,6 +6256,11 @@
           <t>NSE:JUBLFOOD26AUG495CE</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>Closed flat ~15.35 (+0.0% from entry)</t>
+        </is>
+      </c>
       <c r="AC58" t="inlineStr">
         <is>
           <t>2026-08-10 14:02:26</t>
@@ -6240,6 +6355,11 @@
           <t>NSE:MAZDOCK26AUG2550CE</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>Closed down ~77.0 (-4.4% from entry)</t>
+        </is>
+      </c>
       <c r="AC59" t="inlineStr">
         <is>
           <t>2026-08-10 13:39:17</t>
@@ -6334,6 +6454,11 @@
           <t>NSE:RADICO26AUG4600CE</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>Closed down ~111.55 (-6.8% from entry)</t>
+        </is>
+      </c>
       <c r="AC60" t="inlineStr">
         <is>
           <t>2026-08-10 12:53:34</t>
@@ -6428,6 +6553,11 @@
           <t>NSE:COFORGE26AUG1820CE</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>Closed down ~46.6 (-7.3% from entry)</t>
+        </is>
+      </c>
       <c r="AC61" t="inlineStr">
         <is>
           <t>2026-08-10 14:05:13</t>
@@ -6522,6 +6652,11 @@
           <t>NSE:PHOENIXLTD26AUG1940PE</t>
         </is>
       </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>Closed down ~39.4 (-1.9% from entry)</t>
+        </is>
+      </c>
       <c r="AC62" t="inlineStr">
         <is>
           <t>2026-08-10 13:31:27</t>
@@ -6616,6 +6751,11 @@
           <t>NSE:SUZLON26AUG47PE</t>
         </is>
       </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>Closed down ~1.16 (-6.5% from entry)</t>
+        </is>
+      </c>
       <c r="AC63" t="inlineStr">
         <is>
           <t>2026-08-10 14:43:52</t>
@@ -6710,6 +6850,11 @@
           <t>NSE:KAYNES26AUG3750CE</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>Closed down ~75.05 (-16.6% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6799,6 +6944,11 @@
           <t>NSE:PHOENIXLTD26AUG1940PE</t>
         </is>
       </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>Closed down ~38.5 (-4.1% from entry)</t>
+        </is>
+      </c>
       <c r="AC65" t="inlineStr">
         <is>
           <t>2026-08-10 14:07:53</t>
@@ -6888,6 +7038,11 @@
           <t>NSE:BHARATFORG26AUG2080CE</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>Closed down ~58.8 (-14.6% from entry)</t>
+        </is>
+      </c>
       <c r="AC66" t="inlineStr">
         <is>
           <t>2026-08-10 14:57:53</t>
@@ -6982,6 +7137,11 @@
           <t>NSE:BAJFINANCE26AUG1100CE</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>Closed down ~23.75 (-1.2% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7071,6 +7231,11 @@
           <t>NSE:MAZDOCK26AUG2550CE</t>
         </is>
       </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>Closed up ~93.0 (+15.5% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7160,6 +7325,11 @@
           <t>NSE:MCX26AUG2800PE</t>
         </is>
       </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>Closed flat ~90.0 (+0.1% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7249,6 +7419,11 @@
           <t>NSE:JUBLFOOD26AUG495CE</t>
         </is>
       </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>Closed down ~14.75 (-3.9% from entry)</t>
+        </is>
+      </c>
       <c r="AC70" t="inlineStr">
         <is>
           <t>2026-08-10 15:14:47</t>
@@ -7341,6 +7516,11 @@
       <c r="W71" t="inlineStr">
         <is>
           <t>NSE:GRASIM26AUG3380CE</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>Closed up ~104.9 (+5.5% from entry)</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
